--- a/public/cubecode.xlsx
+++ b/public/cubecode.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lh/myProjects/cubefiber/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D41F55-74CD-8C4E-8ED8-925F5FC4BA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4201C59-7167-3D44-A6FD-786EFA40778A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11740" yWindow="5120" windowWidth="43700" windowHeight="28180" activeTab="4" xr2:uid="{0CA53E6B-C3F2-0D46-9617-21A54FC1121D}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9206" uniqueCount="3360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9210" uniqueCount="3364">
   <si>
     <t>corner</t>
   </si>
@@ -32455,6 +32455,22 @@
   </si>
   <si>
     <t>http://www.rubiksplace.com/speedcubing/F2L-algorithms/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FH-qc7pP_pk&amp;list=PL7iQMLIAJ-Yv9stwljAcpCen49hT8BhUr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Left Handed Fast F2L Algorithms &amp; Finger </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://solvethecube.com/algorithms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SolveCube</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -58273,7 +58289,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D3CE84-AC9B-A147-8309-3606006F464C}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -58290,97 +58306,115 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3357</v>
+        <v>3363</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3356</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3355</v>
+        <v>3358</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3354</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>1997</v>
+        <v>3355</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1996</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>2066</v>
+        <v>2000</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2065</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>3318</v>
+        <v>2069</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>3357</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>3356</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>3361</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3360</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{1996406D-8AFF-7241-A49D-CE2258334EFB}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{B9F0FE04-0DFE-664C-AED3-E1AD38459AC1}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{997F97D9-B7FF-2E46-9B9F-9B1B0B1ADF7F}"/>
-    <hyperlink ref="B8" r:id="rId4" xr:uid="{4E419700-7B24-0F4F-A773-E6393A077B02}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{DE18DD20-98B3-6E4B-B3F0-1CCF58380622}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{B492CCA9-C2E6-8D49-9E99-1462A77DD840}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{A1BDFECE-6F27-8F4C-9CCE-1F05A1B2931D}"/>
-    <hyperlink ref="B11" r:id="rId8" xr:uid="{EC48DC90-964F-5241-9596-A81B86E74906}"/>
-    <hyperlink ref="B2" r:id="rId9" xr:uid="{3E7E0E7C-02FB-2B45-91A8-CF8F715592B3}"/>
-    <hyperlink ref="B3" r:id="rId10" xr:uid="{77733918-5498-BB43-9079-EF3C6E24BD2C}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{1996406D-8AFF-7241-A49D-CE2258334EFB}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{B9F0FE04-0DFE-664C-AED3-E1AD38459AC1}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{997F97D9-B7FF-2E46-9B9F-9B1B0B1ADF7F}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{4E419700-7B24-0F4F-A773-E6393A077B02}"/>
+    <hyperlink ref="B10" r:id="rId5" xr:uid="{DE18DD20-98B3-6E4B-B3F0-1CCF58380622}"/>
+    <hyperlink ref="B11" r:id="rId6" xr:uid="{B492CCA9-C2E6-8D49-9E99-1462A77DD840}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{A1BDFECE-6F27-8F4C-9CCE-1F05A1B2931D}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{EC48DC90-964F-5241-9596-A81B86E74906}"/>
+    <hyperlink ref="B3" r:id="rId9" xr:uid="{3E7E0E7C-02FB-2B45-91A8-CF8F715592B3}"/>
+    <hyperlink ref="B4" r:id="rId10" xr:uid="{77733918-5498-BB43-9079-EF3C6E24BD2C}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{DFF19050-F1E1-DC41-99BC-D8C13EF69F6E}"/>
+    <hyperlink ref="B2" r:id="rId12" xr:uid="{F57FCA3A-AD5C-3647-BD0C-C92273FC2864}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
